--- a/data/trans_orig/P21D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94254</t>
+          <t>93682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129062</t>
+          <t>129621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>113133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140862</t>
+          <t>140665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215858</t>
+          <t>217190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261627</t>
+          <t>261957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164728</t>
+          <t>164902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147973</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176966</t>
+          <t>176604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283571</t>
+          <t>284257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>331663</t>
+          <t>329602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>522</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84811</t>
+          <t>77701</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>364195</t>
+          <t>361227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176575</t>
+          <t>177345</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>213368</t>
+          <t>213204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209757</t>
+          <t>216389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>544948</t>
+          <t>543885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>280217</t>
+          <t>283161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>571260</t>
+          <t>575796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>221370</t>
+          <t>223657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258397</t>
+          <t>259350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>533507</t>
+          <t>536817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>885119</t>
+          <t>876930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>57246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91294</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>74990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104591</t>
+          <t>103470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142338</t>
+          <t>141042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183842</t>
+          <t>184241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220092</t>
+          <t>219098</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257892</t>
+          <t>257318</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>205395</t>
+          <t>206024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237680</t>
+          <t>238176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436925</t>
+          <t>438311</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>487197</t>
+          <t>488491</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>40470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160415</t>
+          <t>158409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203234</t>
+          <t>203237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188083</t>
+          <t>187998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>323142</t>
+          <t>339108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>369056</t>
+          <t>369355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>553334</t>
+          <t>561894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199874</t>
+          <t>200524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242901</t>
+          <t>245140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178393</t>
+          <t>163815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305101</t>
+          <t>308580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356963</t>
+          <t>349888</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530655</t>
+          <t>531042</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>44069</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345485</t>
+          <t>362189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>703127</t>
+          <t>704195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>594684</t>
+          <t>593870</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>797464</t>
+          <t>795992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>976637</t>
+          <t>968051</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1382742</t>
+          <t>1394349</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>915549</t>
+          <t>914460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1296494</t>
+          <t>1277927</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>741058</t>
+          <t>743670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>939514</t>
+          <t>937018</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1777611</t>
+          <t>1763700</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2223700</t>
+          <t>2215510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>112217</t>
+          <t>124676</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93682</t>
+          <t>106665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129621</t>
+          <t>143451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>127458</t>
+          <t>141393</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113133</t>
+          <t>126632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140665</t>
+          <t>156287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>239675</t>
+          <t>266069</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217190</t>
+          <t>240459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261957</t>
+          <t>290117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>146259</t>
+          <t>152948</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128546</t>
+          <t>133216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164902</t>
+          <t>170994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>161291</t>
+          <t>171488</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147805</t>
+          <t>156755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176604</t>
+          <t>186687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>307550</t>
+          <t>324436</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284257</t>
+          <t>299327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329602</t>
+          <t>349245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220636</t>
+          <t>255686</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77701</t>
+          <t>229514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361227</t>
+          <t>280124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194958</t>
+          <t>222736</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177345</t>
+          <t>201083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>213204</t>
+          <t>240755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>415594</t>
+          <t>478421</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>216389</t>
+          <t>443629</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>543885</t>
+          <t>509944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>428646</t>
+          <t>203247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283161</t>
+          <t>179082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>575796</t>
+          <t>228621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>240970</t>
+          <t>264652</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223657</t>
+          <t>246398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259350</t>
+          <t>286268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>669616</t>
+          <t>467898</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>536817</t>
+          <t>436977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>876930</t>
+          <t>500846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73069</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57246</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91483</t>
+          <t>117221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89036</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74990</t>
+          <t>85435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103470</t>
+          <t>118059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>162105</t>
+          <t>197297</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141042</t>
+          <t>171259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>225065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>240406</t>
+          <t>259157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219098</t>
+          <t>235138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257318</t>
+          <t>279419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223447</t>
+          <t>256576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>206024</t>
+          <t>240307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>238176</t>
+          <t>273901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>463853</t>
+          <t>515732</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>438311</t>
+          <t>487095</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>488491</t>
+          <t>544148</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>181749</t>
+          <t>200267</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>158409</t>
+          <t>177431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203237</t>
+          <t>223454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>238480</t>
+          <t>192923</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>187998</t>
+          <t>172946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339108</t>
+          <t>212072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>420229</t>
+          <t>393189</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>369355</t>
+          <t>364345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>561894</t>
+          <t>425703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221956</t>
+          <t>227557</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200524</t>
+          <t>204198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245140</t>
+          <t>249937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>259774</t>
+          <t>282484</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>163815</t>
+          <t>262361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308580</t>
+          <t>302798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>481730</t>
+          <t>510041</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349888</t>
+          <t>478674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531042</t>
+          <t>538330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>402</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>587671</t>
+          <t>675695</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>362189</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>704195</t>
+          <t>722066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>649931</t>
+          <t>659282</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>593870</t>
+          <t>622682</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>795992</t>
+          <t>693736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1237602</t>
+          <t>1334977</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>968051</t>
+          <t>1269431</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1394349</t>
+          <t>1394617</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1037267</t>
+          <t>842909</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>914460</t>
+          <t>794740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1277927</t>
+          <t>887212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>885482</t>
+          <t>975199</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>743670</t>
+          <t>940085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>937018</t>
+          <t>1011149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1922749</t>
+          <t>1818108</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1763700</t>
+          <t>1759740</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2215510</t>
+          <t>1878786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
